--- a/data/recon_matrix.xlsx
+++ b/data/recon_matrix.xlsx
@@ -10144,11 +10144,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
@@ -31615,7 +31611,7 @@
         <v>326</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>24</v>
@@ -31636,7 +31632,7 @@
         <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>29</v>
@@ -31657,7 +31653,7 @@
         <v>384</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
         <v>29</v>
@@ -31678,7 +31674,7 @@
         <v>415</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
         <v>34</v>

--- a/data/recon_matrix.xlsx
+++ b/data/recon_matrix.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>563 tools | 53 runnable | 88 web-only (kept) | 32 suggested additions</t>
+          <t>563 tools | 71 runnable | 88 web-only (kept) | 32 suggested additions</t>
         </is>
       </c>
     </row>
@@ -29621,7 +29621,11 @@
           <t>subdomain</t>
         </is>
       </c>
-      <c r="J533" s="5" t="inlineStr"/>
+      <c r="J533" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K533" t="inlineStr">
         <is>
           <t>yes</t>
@@ -29678,8 +29682,16 @@
           <t>any</t>
         </is>
       </c>
-      <c r="J534" s="5" t="inlineStr"/>
-      <c r="K534" t="inlineStr"/>
+      <c r="J534" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr">
         <is>
@@ -29727,8 +29739,16 @@
           <t>tag</t>
         </is>
       </c>
-      <c r="J535" s="5" t="inlineStr"/>
-      <c r="K535" t="inlineStr"/>
+      <c r="J535" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr">
         <is>
@@ -29776,8 +29796,16 @@
           <t>subdomain</t>
         </is>
       </c>
-      <c r="J536" s="5" t="inlineStr"/>
-      <c r="K536" t="inlineStr"/>
+      <c r="J536" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr">
         <is>
@@ -30143,8 +30171,16 @@
           <t>url</t>
         </is>
       </c>
-      <c r="J543" s="5" t="inlineStr"/>
-      <c r="K543" t="inlineStr"/>
+      <c r="J543" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr">
         <is>
@@ -30196,8 +30232,16 @@
           <t>url</t>
         </is>
       </c>
-      <c r="J544" s="5" t="inlineStr"/>
-      <c r="K544" t="inlineStr"/>
+      <c r="J544" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr">
         <is>
@@ -30298,8 +30342,16 @@
           <t>url</t>
         </is>
       </c>
-      <c r="J546" s="5" t="inlineStr"/>
-      <c r="K546" t="inlineStr"/>
+      <c r="J546" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr">
         <is>
@@ -30351,8 +30403,16 @@
           <t>subdomain</t>
         </is>
       </c>
-      <c r="J547" s="5" t="inlineStr"/>
-      <c r="K547" t="inlineStr"/>
+      <c r="J547" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr">
         <is>
@@ -30563,8 +30623,16 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="J551" s="5" t="inlineStr"/>
-      <c r="K551" t="inlineStr"/>
+      <c r="J551" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr">
         <is>
@@ -30612,8 +30680,16 @@
         </is>
       </c>
       <c r="I552" t="inlineStr"/>
-      <c r="J552" s="5" t="inlineStr"/>
-      <c r="K552" t="inlineStr"/>
+      <c r="J552" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr">
         <is>
@@ -30665,8 +30741,16 @@
           <t>endpoint</t>
         </is>
       </c>
-      <c r="J553" s="5" t="inlineStr"/>
-      <c r="K553" t="inlineStr"/>
+      <c r="J553" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr">
         <is>
@@ -30763,8 +30847,16 @@
       </c>
       <c r="H555" t="inlineStr"/>
       <c r="I555" t="inlineStr"/>
-      <c r="J555" s="5" t="inlineStr"/>
-      <c r="K555" t="inlineStr"/>
+      <c r="J555" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr"/>
       <c r="M555" t="inlineStr">
         <is>
@@ -30812,8 +30904,16 @@
           <t>host_port</t>
         </is>
       </c>
-      <c r="J556" s="5" t="inlineStr"/>
-      <c r="K556" t="inlineStr"/>
+      <c r="J556" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
         <is>
@@ -30857,8 +30957,16 @@
       </c>
       <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr"/>
-      <c r="J557" s="5" t="inlineStr"/>
-      <c r="K557" t="inlineStr"/>
+      <c r="J557" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
         <is>
@@ -30910,8 +31018,16 @@
           <t>service</t>
         </is>
       </c>
-      <c r="J558" s="5" t="inlineStr"/>
-      <c r="K558" t="inlineStr"/>
+      <c r="J558" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
         <is>
@@ -31061,8 +31177,16 @@
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
-      <c r="J561" s="5" t="inlineStr"/>
-      <c r="K561" t="inlineStr"/>
+      <c r="J561" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
         <is>
@@ -31110,8 +31234,16 @@
         </is>
       </c>
       <c r="I562" t="inlineStr"/>
-      <c r="J562" s="5" t="inlineStr"/>
-      <c r="K562" t="inlineStr"/>
+      <c r="J562" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
@@ -31159,8 +31291,16 @@
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
-      <c r="J563" s="5" t="inlineStr"/>
-      <c r="K563" t="inlineStr"/>
+      <c r="J563" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
@@ -31611,14 +31751,14 @@
         <v>326</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alienvault-otx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, findomain, fullhunt, gau, gauplus, hackertarget, netlas, paramspider, securitytrails, shodan, subfinder, uncover, urlscan, virustotal, waybackurls, waymore</t>
+          <t>alienvault-otx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, findomain, fullhunt, gau, gauplus, github-subdomains, hackertarget, netlas, paramspider, securitytrails, shodan, subfinder, uncover, urlscan, virustotal, waybackurls, waymore</t>
         </is>
       </c>
     </row>
@@ -31632,14 +31772,14 @@
         <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>alienvault-otx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, findomain, fullhunt, gau, gauplus, hackertarget, httpx, massdns, netlas, paramspider, puredns, securitytrails, shodan, subfinder, subjack, uncover, urlscan, virustotal, waybackurls, waymore</t>
+          <t>alienvault-otx, alterx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, findomain, fullhunt, gau, gauplus, github-subdomains, hackertarget, httpx, massdns, netlas, paramspider, puredns, securitytrails, shodan, subfinder, subjack, uncover, urlscan, virustotal, waybackurls, waymore</t>
         </is>
       </c>
     </row>
@@ -31653,14 +31793,14 @@
         <v>384</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>alienvault-otx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, findomain, fullhunt, gau, gauplus, hackertarget, httpx, massdns, netlas, paramspider, puredns, securitytrails, shodan, subfinder, subjack, uncover, urlscan, virustotal, waybackurls, waymore</t>
+          <t>alienvault-otx, alterx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, feroxbuster, ffuf, findomain, fullhunt, gau, gauplus, github-subdomains, graphw00f, hackertarget, httpx, kiterunner, massdns, netlas, nmap, paramspider, puredns, securitytrails, shodan, sslyze, subfinder, subjack, tlsx, uncover, urlscan, virustotal, waybackurls, waymore</t>
         </is>
       </c>
     </row>
@@ -31674,14 +31814,14 @@
         <v>415</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>alienvault-otx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, findomain, fullhunt, gau, gauplus, gowitness, hackertarget, httpx, katana, massdns, netlas, nuclei, paramspider, puredns, securitytrails, shodan, subfinder, subjack, uncover, urlscan, virustotal, wafw00f, waybackurls, waymore, whatweb</t>
+          <t>alienvault-otx, alterx, amass, asnmap, assetfinder, censys, certspotter, chaos, criminal-ip, crt-sh, dnsx, feroxbuster, ffuf, findomain, fullhunt, gau, gauplus, gf, github-subdomains, gowitness, graphw00f, hackertarget, httpx, katana, kiterunner, massdns, netlas, nmap, nuclei, paramspider, puredns, securitytrails, shodan, sslyze, subfinder, subjack, tlsx, uncover, unfurl, urlscan, virustotal, wafw00f, waybackurls, waymore, whatweb</t>
         </is>
       </c>
     </row>
@@ -31775,14 +31915,14 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>linkfinder, secretfinder</t>
+          <t>jsluice, linkfinder, secretfinder</t>
         </is>
       </c>
     </row>
